--- a/SalesReport/Andmetabeli kirjeldus - ProductTable.xlsx
+++ b/SalesReport/Andmetabeli kirjeldus - ProductTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sipsik\Documents\andmetarkus2026\SalesReport\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C92495-BD08-4A7A-BA80-2F54CBB150AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C233C4B2-EAF5-4925-89A2-F8292FA9EB08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5FDADF70-75BA-4EB4-A4F1-A6770464B2AE}"/>
   </bookViews>
@@ -95,7 +95,7 @@
     <t>Kategooria nimetus</t>
   </si>
   <si>
-    <t>Toote tootja ettevõtte nimi</t>
+    <t>Toote tootja ettevõtte nimi, mis pärineb äriregistrist</t>
   </si>
 </sst>
 </file>
